--- a/solutions/ess-maker-skills/src/skills/setup/workday-da/assets/workday-admin-handoff.xlsx
+++ b/solutions/ess-maker-skills/src/skills/setup/workday-da/assets/workday-admin-handoff.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm the policy applies to the ESS OAuth client identity and allows SAML for the intended employees. Record whether that rule was already active or a reviewed policy was activated.</t>
+          <t xml:space="preserve">Confirm the policy applies to the ESS OAuth client identity and allows SAML for the intended employees. Enter exactly one of: An existing active policy scopes the ESS OAuth client and allows SAML for the intended employees; A reviewed policy scoped to the ESS OAuth client was activated</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record the configured employee population.</t>
+          <t xml:space="preserve">Record the configured employee population. Enter exactly one of: Entire workforce - All Employees access is configured; Limited or test population - the intended Workday security group and test employee access are configured</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
